--- a/artfynd/A 41606-2025 artfynd.xlsx
+++ b/artfynd/A 41606-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>65886608</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>V om Lilla Bolandet, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630328.7456729272</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6652637.962436358</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Fattiga-medelrika sumpskogar och smärre halvöppna kärrytor i ett knappt 1 km långt öst-västligt stråk</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>
